--- a/base.xlsx
+++ b/base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Documentos\Python Scripts\Fantasy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF445CFA-7ED6-48ED-8980-A3A7B747D75B}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="1350" windowWidth="21600" windowHeight="11835" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="466">
   <si>
     <t>player_id</t>
   </si>
@@ -1441,6 +1441,12 @@
   </si>
   <si>
     <t>l</t>
+  </si>
+  <si>
+    <t>Darryn Peterson</t>
+  </si>
+  <si>
+    <t>Keaton Wagler</t>
   </si>
 </sst>
 </file>
@@ -14912,11 +14918,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B408" s="1"/>
+    <row r="408" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E408" s="1">
+        <v>18</v>
+      </c>
+      <c r="F408" s="1">
+        <v>3</v>
+      </c>
+      <c r="G408" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="H408" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I408" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J408" s="1">
+        <v>1</v>
+      </c>
+      <c r="K408" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B409" s="1"/>
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E409" s="1">
+        <v>16</v>
+      </c>
+      <c r="F409" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="G409" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="H409" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I409" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J409" s="1">
+        <v>2</v>
+      </c>
+      <c r="K409" s="1">
+        <v>2.2999999999999998</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K407" xr:uid="{CEDFA625-895D-46B5-9149-0741A5E1C2FB}">
@@ -15087,10 +15151,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19E893F-F6CA-495F-B37D-0D5DEFFEED8B}">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -15107,7 +15171,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>7</v>
       </c>
@@ -15120,8 +15184,12 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="str">
+        <f>VLOOKUP(B2,players!A:B,2)</f>
+        <v>Anthony Davis</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7</v>
       </c>
@@ -15134,8 +15202,12 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="str">
+        <f>VLOOKUP(B3,players!A:B,2)</f>
+        <v>Kel'el Ware</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>7</v>
       </c>
@@ -15148,8 +15220,12 @@
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="str">
+        <f>VLOOKUP(B4,players!A:B,2)</f>
+        <v>Ausar Thompson</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
@@ -15162,8 +15238,12 @@
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="str">
+        <f>VLOOKUP(B5,players!A:B,2)</f>
+        <v>Ja Morant</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7</v>
       </c>
@@ -15176,8 +15256,12 @@
       <c r="D6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="str">
+        <f>VLOOKUP(B6,players!A:B,2)</f>
+        <v>Scottie Barnes</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -15190,8 +15274,12 @@
       <c r="D7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="str">
+        <f>VLOOKUP(B7,players!A:B,2)</f>
+        <v>Dejounte Murray</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -15204,8 +15292,12 @@
       <c r="D8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="str">
+        <f>VLOOKUP(B8,players!A:B,2)</f>
+        <v>Onyeka Okongwu</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -15218,13 +15310,17 @@
       <c r="D9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="str">
+        <f>VLOOKUP(B9,players!A:B,2)</f>
+        <v>Matas Buzelis</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10">
-        <v>128</v>
+        <v>407</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -15232,8 +15328,12 @@
       <c r="D10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="str">
+        <f>VLOOKUP(B10,players!A:B,2)</f>
+        <v>Darryn Peterson</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -15246,13 +15346,17 @@
       <c r="D11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="str">
+        <f>VLOOKUP(B11,players!A:B,2)</f>
+        <v>Tyrese Maxey</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12">
-        <v>181</v>
+        <v>408</v>
       </c>
       <c r="C12" t="s">
         <v>462</v>
@@ -15260,13 +15364,17 @@
       <c r="D12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="str">
+        <f>VLOOKUP(B12,players!A:B,2)</f>
+        <v>Keaton Wagler</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13">
-        <v>205</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
         <v>25</v>
@@ -15274,8 +15382,12 @@
       <c r="D13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="str">
+        <f>VLOOKUP(B13,players!A:B,2)</f>
+        <v>Anthony Edwards</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -15288,8 +15400,12 @@
       <c r="D14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="str">
+        <f>VLOOKUP(B14,players!A:B,2)</f>
+        <v>Alperen Şengün</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -15302,13 +15418,17 @@
       <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="str">
+        <f>VLOOKUP(B15,players!A:B,2)</f>
+        <v>Kevin Durant</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>25</v>
@@ -15316,8 +15436,12 @@
       <c r="D16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F16" t="str">
+        <f>VLOOKUP(B16,players!A:B,2)</f>
+        <v>Michael Porter Jr.</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -15330,8 +15454,12 @@
       <c r="D17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F17" t="str">
+        <f>VLOOKUP(B17,players!A:B,2)</f>
+        <v>Jalen Green</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -15344,8 +15472,12 @@
       <c r="D18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F18" t="str">
+        <f>VLOOKUP(B18,players!A:B,2)</f>
+        <v>Tyler Herro</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -15358,8 +15490,12 @@
       <c r="D19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F19" t="str">
+        <f>VLOOKUP(B19,players!A:B,2)</f>
+        <v>Trae Young</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -15372,8 +15508,12 @@
       <c r="D20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F20" t="str">
+        <f>VLOOKUP(B20,players!A:B,2)</f>
+        <v>Jalen Duren</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -15386,8 +15526,12 @@
       <c r="D21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F21" t="str">
+        <f>VLOOKUP(B21,players!A:B,2)</f>
+        <v>Luka Dončić</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -15400,8 +15544,12 @@
       <c r="D22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F22" t="str">
+        <f>VLOOKUP(B22,players!A:B,2)</f>
+        <v>Kawhi Leonard</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -15414,8 +15562,12 @@
       <c r="D23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F23" t="str">
+        <f>VLOOKUP(B23,players!A:B,2)</f>
+        <v>Jaren Jackson Jr.</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -15428,8 +15580,12 @@
       <c r="D24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F24" t="str">
+        <f>VLOOKUP(B24,players!A:B,2)</f>
+        <v>OG Anunoby</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -15442,8 +15598,12 @@
       <c r="D25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F25" t="str">
+        <f>VLOOKUP(B25,players!A:B,2)</f>
+        <v>Kyrie Irving</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -15456,8 +15616,12 @@
       <c r="D26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F26" t="str">
+        <f>VLOOKUP(B26,players!A:B,2)</f>
+        <v>Bam Adebayo</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -15470,8 +15634,12 @@
       <c r="D27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F27" t="str">
+        <f>VLOOKUP(B27,players!A:B,2)</f>
+        <v>Jaylen Brown</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -15484,8 +15652,12 @@
       <c r="D28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F28" t="str">
+        <f>VLOOKUP(B28,players!A:B,2)</f>
+        <v>Stephon Castle</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -15498,8 +15670,12 @@
       <c r="D29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F29" t="str">
+        <f>VLOOKUP(B29,players!A:B,2)</f>
+        <v>Franz Wagner</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
@@ -15512,8 +15688,12 @@
       <c r="D30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F30" t="str">
+        <f>VLOOKUP(B30,players!A:B,2)</f>
+        <v>Donovan Mitchell</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -15526,8 +15706,12 @@
       <c r="D31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F31" t="str">
+        <f>VLOOKUP(B31,players!A:B,2)</f>
+        <v>DeMar DeRozan</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -15540,8 +15724,12 @@
       <c r="D32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F32" t="str">
+        <f>VLOOKUP(B32,players!A:B,2)</f>
+        <v>Joel Embiid</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>5</v>
       </c>
@@ -15554,8 +15742,12 @@
       <c r="D33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F33" t="str">
+        <f>VLOOKUP(B33,players!A:B,2)</f>
+        <v>Giannis Antetokounmpo</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -15568,8 +15760,12 @@
       <c r="D34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F34" t="str">
+        <f>VLOOKUP(B34,players!A:B,2)</f>
+        <v>VJ Edgecombe</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -15582,13 +15778,17 @@
       <c r="D35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F35" t="str">
+        <f>VLOOKUP(B35,players!A:B,2)</f>
+        <v>James Harden</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>25</v>
@@ -15596,8 +15796,12 @@
       <c r="D36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F36" t="str">
+        <f>VLOOKUP(B36,players!A:B,2)</f>
+        <v>Brandon Miller</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5</v>
       </c>
@@ -15610,8 +15814,12 @@
       <c r="D37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F37" t="str">
+        <f>VLOOKUP(B37,players!A:B,2)</f>
+        <v>Naz Reid</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -15624,13 +15832,17 @@
       <c r="D38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F38" t="str">
+        <f>VLOOKUP(B38,players!A:B,2)</f>
+        <v>Nikola Jokić</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>24</v>
@@ -15638,8 +15850,12 @@
       <c r="D39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F39" t="str">
+        <f>VLOOKUP(B39,players!A:B,2)</f>
+        <v>Paul George</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -15652,8 +15868,12 @@
       <c r="D40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F40" t="str">
+        <f>VLOOKUP(B40,players!A:B,2)</f>
+        <v>Miles Bridges</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>6</v>
       </c>
@@ -15666,8 +15886,12 @@
       <c r="D41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F41" t="str">
+        <f>VLOOKUP(B41,players!A:B,2)</f>
+        <v>Cade Cunningham</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>6</v>
       </c>
@@ -15680,8 +15904,12 @@
       <c r="D42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F42" t="str">
+        <f>VLOOKUP(B42,players!A:B,2)</f>
+        <v>Derrick White</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>6</v>
       </c>
@@ -15694,8 +15922,12 @@
       <c r="D43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F43" t="str">
+        <f>VLOOKUP(B43,players!A:B,2)</f>
+        <v>Keyonte George</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
@@ -15708,8 +15940,12 @@
       <c r="D44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F44" t="str">
+        <f>VLOOKUP(B44,players!A:B,2)</f>
+        <v>Donovan Clingan</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -15722,8 +15958,12 @@
       <c r="D45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F45" t="str">
+        <f>VLOOKUP(B45,players!A:B,2)</f>
+        <v>Jalen Johnson</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>8</v>
       </c>
@@ -15736,8 +15976,12 @@
       <c r="D46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F46" t="str">
+        <f>VLOOKUP(B46,players!A:B,2)</f>
+        <v>Trey Murphy III</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>8</v>
       </c>
@@ -15750,8 +15994,12 @@
       <c r="D47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F47" t="str">
+        <f>VLOOKUP(B47,players!A:B,2)</f>
+        <v>Zion Williamson</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>8</v>
       </c>
@@ -15764,13 +16012,17 @@
       <c r="D48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F48" t="str">
+        <f>VLOOKUP(B48,players!A:B,2)</f>
+        <v>De'Aaron Fox</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>8</v>
       </c>
       <c r="B49">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>27</v>
@@ -15778,8 +16030,12 @@
       <c r="D49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F49" t="str">
+        <f>VLOOKUP(B49,players!A:B,2)</f>
+        <v>Josh Hart</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>9</v>
       </c>
@@ -15792,8 +16048,12 @@
       <c r="D50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F50" t="str">
+        <f>VLOOKUP(B50,players!A:B,2)</f>
+        <v>Jayson Tatum</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>9</v>
       </c>
@@ -15806,8 +16066,12 @@
       <c r="D51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F51" t="str">
+        <f>VLOOKUP(B51,players!A:B,2)</f>
+        <v>Jarrett Allen</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>9</v>
       </c>
@@ -15820,8 +16084,12 @@
       <c r="D52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F52" t="str">
+        <f>VLOOKUP(B52,players!A:B,2)</f>
+        <v>Brandon Ingram</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>9</v>
       </c>
@@ -15834,8 +16102,12 @@
       <c r="D53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F53" t="str">
+        <f>VLOOKUP(B53,players!A:B,2)</f>
+        <v>Shaedon Sharpe</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>9</v>
       </c>
@@ -15848,8 +16120,12 @@
       <c r="D54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F54" t="str">
+        <f>VLOOKUP(B54,players!A:B,2)</f>
+        <v>Stephen Curry</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9</v>
       </c>
@@ -15862,13 +16138,17 @@
       <c r="D55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F55" t="str">
+        <f>VLOOKUP(B55,players!A:B,2)</f>
+        <v>Darius Garland</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10</v>
       </c>
       <c r="B56">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>23</v>
@@ -15876,8 +16156,12 @@
       <c r="D56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F56" t="str">
+        <f>VLOOKUP(B56,players!A:B,2)</f>
+        <v>Walker Kessler</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>10</v>
       </c>
@@ -15890,8 +16174,12 @@
       <c r="D57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F57" t="str">
+        <f>VLOOKUP(B57,players!A:B,2)</f>
+        <v>Alex Sarr</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>10</v>
       </c>
@@ -15904,8 +16192,12 @@
       <c r="D58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F58" t="str">
+        <f>VLOOKUP(B58,players!A:B,2)</f>
+        <v>Julius Randle</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10</v>
       </c>
@@ -15918,8 +16210,12 @@
       <c r="D59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F59" t="str">
+        <f>VLOOKUP(B59,players!A:B,2)</f>
+        <v>Jalen Williams</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>10</v>
       </c>
@@ -15932,8 +16228,12 @@
       <c r="D60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F60" t="str">
+        <f>VLOOKUP(B60,players!A:B,2)</f>
+        <v>Jamal Murray</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>10</v>
       </c>
@@ -15946,8 +16246,12 @@
       <c r="D61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F61" t="str">
+        <f>VLOOKUP(B61,players!A:B,2)</f>
+        <v>Jalen Brunson</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>11</v>
       </c>
@@ -15960,8 +16264,12 @@
       <c r="D62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F62" t="str">
+        <f>VLOOKUP(B62,players!A:B,2)</f>
+        <v>Domantas Sabonis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>11</v>
       </c>
@@ -15974,8 +16282,12 @@
       <c r="D63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F63" t="str">
+        <f>VLOOKUP(B63,players!A:B,2)</f>
+        <v>Desmond Bane</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>11</v>
       </c>
@@ -15988,8 +16300,12 @@
       <c r="D64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F64" t="str">
+        <f>VLOOKUP(B64,players!A:B,2)</f>
+        <v>Amen Thompson</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>11</v>
       </c>
@@ -16002,8 +16318,12 @@
       <c r="D65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F65" t="str">
+        <f>VLOOKUP(B65,players!A:B,2)</f>
+        <v>Shai Gilgeous-Alexander</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>11</v>
       </c>
@@ -16016,13 +16336,17 @@
       <c r="D66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F66" t="str">
+        <f>VLOOKUP(B66,players!A:B,2)</f>
+        <v>CJ McCollum</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>11</v>
       </c>
       <c r="B67">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>462</v>
@@ -16030,8 +16354,12 @@
       <c r="D67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F67" t="str">
+        <f>VLOOKUP(B67,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>12</v>
       </c>
@@ -16044,8 +16372,12 @@
       <c r="D68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F68" t="str">
+        <f>VLOOKUP(B68,players!A:B,2)</f>
+        <v>Chet Holmgren</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>12</v>
       </c>
@@ -16058,8 +16390,12 @@
       <c r="D69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F69" t="str">
+        <f>VLOOKUP(B69,players!A:B,2)</f>
+        <v>Lauri Markkanen</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>12</v>
       </c>
@@ -16072,8 +16408,12 @@
       <c r="D70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F70" t="str">
+        <f>VLOOKUP(B70,players!A:B,2)</f>
+        <v>Devin Booker</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>12</v>
       </c>
@@ -16086,13 +16426,17 @@
       <c r="D71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F71" t="str">
+        <f>VLOOKUP(B71,players!A:B,2)</f>
+        <v>Tyrese Haliburton</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>12</v>
       </c>
       <c r="B72">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>462</v>
@@ -16100,8 +16444,12 @@
       <c r="D72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F72" t="str">
+        <f>VLOOKUP(B72,players!A:B,2)</f>
+        <v>Paolo Banchero</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>12</v>
       </c>
@@ -16114,8 +16462,12 @@
       <c r="D73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F73" t="str">
+        <f>VLOOKUP(B73,players!A:B,2)</f>
+        <v>Kevin Porter Jr.</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>13</v>
       </c>
@@ -16128,8 +16480,12 @@
       <c r="D74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F74" t="str">
+        <f>VLOOKUP(B74,players!A:B,2)</f>
+        <v>Victor Wembanyama</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>13</v>
       </c>
@@ -16142,8 +16498,12 @@
       <c r="D75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F75" t="str">
+        <f>VLOOKUP(B75,players!A:B,2)</f>
+        <v>Josh Giddey</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>13</v>
       </c>
@@ -16156,8 +16516,12 @@
       <c r="D76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F76" t="str">
+        <f>VLOOKUP(B76,players!A:B,2)</f>
+        <v>Deni Avdija</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>13</v>
       </c>
@@ -16170,13 +16534,17 @@
       <c r="D77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F77" t="str">
+        <f>VLOOKUP(B77,players!A:B,2)</f>
+        <v>Pascal Siakam</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>13</v>
       </c>
       <c r="B78">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>462</v>
@@ -16184,8 +16552,12 @@
       <c r="D78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F78" t="str">
+        <f>VLOOKUP(B78,players!A:B,2)</f>
+        <v>Ivica Zubac</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>13</v>
       </c>
@@ -16198,8 +16570,12 @@
       <c r="D79">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F79" t="str">
+        <f>VLOOKUP(B79,players!A:B,2)</f>
+        <v>Austin Reaves</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>14</v>
       </c>
@@ -16212,8 +16588,12 @@
       <c r="D80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F80" t="str">
+        <f>VLOOKUP(B80,players!A:B,2)</f>
+        <v>Evan Mobley</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>14</v>
       </c>
@@ -16226,8 +16606,12 @@
       <c r="D81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F81" t="str">
+        <f>VLOOKUP(B81,players!A:B,2)</f>
+        <v>LeBron James</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>14</v>
       </c>
@@ -16240,13 +16624,17 @@
       <c r="D82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F82" t="str">
+        <f>VLOOKUP(B82,players!A:B,2)</f>
+        <v>Cooper Flagg</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>14</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>462</v>
@@ -16254,13 +16642,17 @@
       <c r="D83">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F83" t="str">
+        <f>VLOOKUP(B83,players!A:B,2)</f>
+        <v>Moussa Diabaté</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>14</v>
       </c>
       <c r="B84">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>27</v>
@@ -16268,8 +16660,12 @@
       <c r="D84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F84" t="str">
+        <f>VLOOKUP(B84,players!A:B,2)</f>
+        <v>Coby White</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>14</v>
       </c>
@@ -16281,6 +16677,10 @@
       </c>
       <c r="D85">
         <v>1</v>
+      </c>
+      <c r="F85" t="str">
+        <f>VLOOKUP(B85,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
       </c>
     </row>
   </sheetData>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF445CFA-7ED6-48ED-8980-A3A7B747D75B}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E206A74-3F03-4526-A53B-C9EF8018D802}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -1511,6 +1511,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15212,7 +15216,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -15222,7 +15226,7 @@
       </c>
       <c r="F4" t="str">
         <f>VLOOKUP(B4,players!A:B,2)</f>
-        <v>Ausar Thompson</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -15446,7 +15450,7 @@
         <v>2</v>
       </c>
       <c r="B17">
-        <v>219</v>
+        <v>107</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>462</v>
@@ -15456,7 +15460,7 @@
       </c>
       <c r="F17" t="str">
         <f>VLOOKUP(B17,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>RJ Barrett</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -15842,7 +15846,7 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>24</v>
@@ -15852,7 +15856,7 @@
       </c>
       <c r="F39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -16022,7 +16026,7 @@
         <v>8</v>
       </c>
       <c r="B49">
-        <v>45</v>
+        <v>237</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>27</v>
@@ -16032,7 +16036,7 @@
       </c>
       <c r="F49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -16346,7 +16350,7 @@
         <v>11</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>462</v>
@@ -16356,7 +16360,7 @@
       </c>
       <c r="F67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -16634,7 +16638,7 @@
         <v>14</v>
       </c>
       <c r="B83">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>462</v>
@@ -16644,7 +16648,7 @@
       </c>
       <c r="F83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E206A74-3F03-4526-A53B-C9EF8018D802}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA3C96F-E38F-49C4-BB1E-EEF100BB9266}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
@@ -15756,7 +15756,7 @@
         <v>5</v>
       </c>
       <c r="B34">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>462</v>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="F34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>VJ Edgecombe</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -15864,7 +15864,7 @@
         <v>6</v>
       </c>
       <c r="B40">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>25</v>
@@ -15874,7 +15874,7 @@
       </c>
       <c r="F40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -15882,7 +15882,7 @@
         <v>6</v>
       </c>
       <c r="B41">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>462</v>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="F41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -15900,7 +15900,7 @@
         <v>6</v>
       </c>
       <c r="B42">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>26</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="F42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">

--- a/base.xlsx
+++ b/base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA3C96F-E38F-49C4-BB1E-EEF100BB9266}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C45A6797-42A0-4171-A9C7-65F49BA60135}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="scenario_moves" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">players!$A$1:$K$407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">players!$A$1:$K$409</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="465">
   <si>
     <t>player_id</t>
   </si>
@@ -1438,9 +1438,6 @@
   </si>
   <si>
     <t>UTIL</t>
-  </si>
-  <si>
-    <t>l</t>
   </si>
   <si>
     <t>Darryn Peterson</t>
@@ -8660,8 +8657,8 @@
       <c r="F212" s="1">
         <v>3.7</v>
       </c>
-      <c r="G212" s="1" t="s">
-        <v>463</v>
+      <c r="G212" s="1">
+        <v>6.1</v>
       </c>
       <c r="H212" s="1">
         <v>1.1000000000000001</v>
@@ -14927,7 +14924,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>27</v>
@@ -14959,7 +14956,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>26</v>
@@ -14987,9 +14984,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K407" xr:uid="{CEDFA625-895D-46B5-9149-0741A5E1C2FB}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K407">
-      <sortCondition ref="A1:A407"/>
+  <autoFilter ref="A1:K409" xr:uid="{CEDFA625-895D-46B5-9149-0741A5E1C2FB}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K409">
+      <sortCondition ref="A1:A409"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
